--- a/data/Инфляция и ключевая ставка Банка России.xlsx
+++ b/data/Инфляция и ключевая ставка Банка России.xlsx
@@ -85,14 +85,14 @@
     <x:row r="2">
       <x:c r="A2" s="0" t="inlineStr">
         <x:is>
-          <x:t>08.2025</x:t>
+          <x:t>02.2026</x:t>
         </x:is>
       </x:c>
       <x:c r="B2" s="3" t="n">
-        <x:v>18.00</x:v>
+        <x:v>15.50</x:v>
       </x:c>
       <x:c r="C2" s="3" t="n">
-        <x:v>8.14</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="D2" s="3" t="n">
         <x:v>4.00</x:v>
@@ -101,14 +101,14 @@
     <x:row r="3">
       <x:c r="A3" s="0" t="inlineStr">
         <x:is>
-          <x:t>07.2025</x:t>
+          <x:t>01.2026</x:t>
         </x:is>
       </x:c>
       <x:c r="B3" s="3" t="n">
-        <x:v>18.00</x:v>
+        <x:v>16.00</x:v>
       </x:c>
       <x:c r="C3" s="3" t="n">
-        <x:v>8.79</x:v>
+        <x:v>6.00</x:v>
       </x:c>
       <x:c r="D3" s="3" t="n">
         <x:v>4.00</x:v>
@@ -117,14 +117,14 @@
     <x:row r="4">
       <x:c r="A4" s="0" t="inlineStr">
         <x:is>
-          <x:t>06.2025</x:t>
+          <x:t>12.2025</x:t>
         </x:is>
       </x:c>
       <x:c r="B4" s="3" t="n">
-        <x:v>20.00</x:v>
+        <x:v>16.00</x:v>
       </x:c>
       <x:c r="C4" s="3" t="n">
-        <x:v>9.40</x:v>
+        <x:v>5.59</x:v>
       </x:c>
       <x:c r="D4" s="3" t="n">
         <x:v>4.00</x:v>
@@ -133,14 +133,14 @@
     <x:row r="5">
       <x:c r="A5" s="0" t="inlineStr">
         <x:is>
-          <x:t>05.2025</x:t>
+          <x:t>11.2025</x:t>
         </x:is>
       </x:c>
       <x:c r="B5" s="3" t="n">
-        <x:v>21.00</x:v>
+        <x:v>16.50</x:v>
       </x:c>
       <x:c r="C5" s="3" t="n">
-        <x:v>9.88</x:v>
+        <x:v>6.64</x:v>
       </x:c>
       <x:c r="D5" s="3" t="n">
         <x:v>4.00</x:v>
@@ -149,14 +149,14 @@
     <x:row r="6">
       <x:c r="A6" s="0" t="inlineStr">
         <x:is>
-          <x:t>04.2025</x:t>
+          <x:t>10.2025</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" s="3" t="n">
-        <x:v>21.00</x:v>
+        <x:v>16.50</x:v>
       </x:c>
       <x:c r="C6" s="3" t="n">
-        <x:v>10.23</x:v>
+        <x:v>7.71</x:v>
       </x:c>
       <x:c r="D6" s="3" t="n">
         <x:v>4.00</x:v>
@@ -165,14 +165,14 @@
     <x:row r="7">
       <x:c r="A7" s="0" t="inlineStr">
         <x:is>
-          <x:t>03.2025</x:t>
+          <x:t>09.2025</x:t>
         </x:is>
       </x:c>
       <x:c r="B7" s="3" t="n">
-        <x:v>21.00</x:v>
+        <x:v>17.00</x:v>
       </x:c>
       <x:c r="C7" s="3" t="n">
-        <x:v>10.34</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="D7" s="3" t="n">
         <x:v>4.00</x:v>
@@ -181,14 +181,14 @@
     <x:row r="8">
       <x:c r="A8" s="0" t="inlineStr">
         <x:is>
-          <x:t>02.2025</x:t>
+          <x:t>08.2025</x:t>
         </x:is>
       </x:c>
       <x:c r="B8" s="3" t="n">
-        <x:v>21.00</x:v>
+        <x:v>18.00</x:v>
       </x:c>
       <x:c r="C8" s="3" t="n">
-        <x:v>10.06</x:v>
+        <x:v>8.14</x:v>
       </x:c>
       <x:c r="D8" s="3" t="n">
         <x:v>4.00</x:v>
@@ -197,14 +197,14 @@
     <x:row r="9">
       <x:c r="A9" s="0" t="inlineStr">
         <x:is>
-          <x:t>01.2025</x:t>
+          <x:t>07.2025</x:t>
         </x:is>
       </x:c>
       <x:c r="B9" s="3" t="n">
-        <x:v>21.00</x:v>
+        <x:v>18.00</x:v>
       </x:c>
       <x:c r="C9" s="3" t="n">
-        <x:v>9.92</x:v>
+        <x:v>8.79</x:v>
       </x:c>
       <x:c r="D9" s="3" t="n">
         <x:v>4.00</x:v>
@@ -213,14 +213,14 @@
     <x:row r="10">
       <x:c r="A10" s="0" t="inlineStr">
         <x:is>
-          <x:t>12.2024</x:t>
+          <x:t>06.2025</x:t>
         </x:is>
       </x:c>
       <x:c r="B10" s="3" t="n">
-        <x:v>21.00</x:v>
+        <x:v>20.00</x:v>
       </x:c>
       <x:c r="C10" s="3" t="n">
-        <x:v>9.52</x:v>
+        <x:v>9.40</x:v>
       </x:c>
       <x:c r="D10" s="3" t="n">
         <x:v>4.00</x:v>
@@ -229,14 +229,14 @@
     <x:row r="11">
       <x:c r="A11" s="0" t="inlineStr">
         <x:is>
-          <x:t>11.2024</x:t>
+          <x:t>05.2025</x:t>
         </x:is>
       </x:c>
       <x:c r="B11" s="3" t="n">
         <x:v>21.00</x:v>
       </x:c>
       <x:c r="C11" s="3" t="n">
-        <x:v>8.88</x:v>
+        <x:v>9.88</x:v>
       </x:c>
       <x:c r="D11" s="3" t="n">
         <x:v>4.00</x:v>
@@ -245,14 +245,14 @@
     <x:row r="12">
       <x:c r="A12" s="0" t="inlineStr">
         <x:is>
-          <x:t>10.2024</x:t>
+          <x:t>04.2025</x:t>
         </x:is>
       </x:c>
       <x:c r="B12" s="3" t="n">
         <x:v>21.00</x:v>
       </x:c>
       <x:c r="C12" s="3" t="n">
-        <x:v>8.54</x:v>
+        <x:v>10.23</x:v>
       </x:c>
       <x:c r="D12" s="3" t="n">
         <x:v>4.00</x:v>
@@ -261,14 +261,14 @@
     <x:row r="13">
       <x:c r="A13" s="0" t="inlineStr">
         <x:is>
-          <x:t>09.2024</x:t>
+          <x:t>03.2025</x:t>
         </x:is>
       </x:c>
       <x:c r="B13" s="3" t="n">
-        <x:v>19.00</x:v>
+        <x:v>21.00</x:v>
       </x:c>
       <x:c r="C13" s="3" t="n">
-        <x:v>8.63</x:v>
+        <x:v>10.34</x:v>
       </x:c>
       <x:c r="D13" s="3" t="n">
         <x:v>4.00</x:v>
@@ -277,14 +277,14 @@
     <x:row r="14">
       <x:c r="A14" s="0" t="inlineStr">
         <x:is>
-          <x:t>08.2024</x:t>
+          <x:t>02.2025</x:t>
         </x:is>
       </x:c>
       <x:c r="B14" s="3" t="n">
-        <x:v>18.00</x:v>
+        <x:v>21.00</x:v>
       </x:c>
       <x:c r="C14" s="3" t="n">
-        <x:v>9.05</x:v>
+        <x:v>10.06</x:v>
       </x:c>
       <x:c r="D14" s="3" t="n">
         <x:v>4.00</x:v>
@@ -293,14 +293,14 @@
     <x:row r="15">
       <x:c r="A15" s="0" t="inlineStr">
         <x:is>
-          <x:t>07.2024</x:t>
+          <x:t>01.2025</x:t>
         </x:is>
       </x:c>
       <x:c r="B15" s="3" t="n">
-        <x:v>18.00</x:v>
+        <x:v>21.00</x:v>
       </x:c>
       <x:c r="C15" s="3" t="n">
-        <x:v>9.13</x:v>
+        <x:v>9.92</x:v>
       </x:c>
       <x:c r="D15" s="3" t="n">
         <x:v>4.00</x:v>
@@ -309,14 +309,14 @@
     <x:row r="16">
       <x:c r="A16" s="0" t="inlineStr">
         <x:is>
-          <x:t>06.2024</x:t>
+          <x:t>12.2024</x:t>
         </x:is>
       </x:c>
       <x:c r="B16" s="3" t="n">
-        <x:v>16.00</x:v>
+        <x:v>21.00</x:v>
       </x:c>
       <x:c r="C16" s="3" t="n">
-        <x:v>8.59</x:v>
+        <x:v>9.52</x:v>
       </x:c>
       <x:c r="D16" s="3" t="n">
         <x:v>4.00</x:v>
@@ -325,14 +325,14 @@
     <x:row r="17">
       <x:c r="A17" s="0" t="inlineStr">
         <x:is>
-          <x:t>05.2024</x:t>
+          <x:t>11.2024</x:t>
         </x:is>
       </x:c>
       <x:c r="B17" s="3" t="n">
-        <x:v>16.00</x:v>
+        <x:v>21.00</x:v>
       </x:c>
       <x:c r="C17" s="3" t="n">
-        <x:v>8.30</x:v>
+        <x:v>8.88</x:v>
       </x:c>
       <x:c r="D17" s="3" t="n">
         <x:v>4.00</x:v>
@@ -341,14 +341,14 @@
     <x:row r="18">
       <x:c r="A18" s="0" t="inlineStr">
         <x:is>
-          <x:t>04.2024</x:t>
+          <x:t>10.2024</x:t>
         </x:is>
       </x:c>
       <x:c r="B18" s="3" t="n">
-        <x:v>16.00</x:v>
+        <x:v>21.00</x:v>
       </x:c>
       <x:c r="C18" s="3" t="n">
-        <x:v>7.84</x:v>
+        <x:v>8.54</x:v>
       </x:c>
       <x:c r="D18" s="3" t="n">
         <x:v>4.00</x:v>
@@ -357,14 +357,14 @@
     <x:row r="19">
       <x:c r="A19" s="0" t="inlineStr">
         <x:is>
-          <x:t>03.2024</x:t>
+          <x:t>09.2024</x:t>
         </x:is>
       </x:c>
       <x:c r="B19" s="3" t="n">
-        <x:v>16.00</x:v>
+        <x:v>19.00</x:v>
       </x:c>
       <x:c r="C19" s="3" t="n">
-        <x:v>7.72</x:v>
+        <x:v>8.63</x:v>
       </x:c>
       <x:c r="D19" s="3" t="n">
         <x:v>4.00</x:v>
@@ -373,14 +373,14 @@
     <x:row r="20">
       <x:c r="A20" s="0" t="inlineStr">
         <x:is>
-          <x:t>02.2024</x:t>
+          <x:t>08.2024</x:t>
         </x:is>
       </x:c>
       <x:c r="B20" s="3" t="n">
-        <x:v>16.00</x:v>
+        <x:v>18.00</x:v>
       </x:c>
       <x:c r="C20" s="3" t="n">
-        <x:v>7.69</x:v>
+        <x:v>9.05</x:v>
       </x:c>
       <x:c r="D20" s="3" t="n">
         <x:v>4.00</x:v>
@@ -389,14 +389,14 @@
     <x:row r="21">
       <x:c r="A21" s="0" t="inlineStr">
         <x:is>
-          <x:t>01.2024</x:t>
+          <x:t>07.2024</x:t>
         </x:is>
       </x:c>
       <x:c r="B21" s="3" t="n">
-        <x:v>16.00</x:v>
+        <x:v>18.00</x:v>
       </x:c>
       <x:c r="C21" s="3" t="n">
-        <x:v>7.44</x:v>
+        <x:v>9.13</x:v>
       </x:c>
       <x:c r="D21" s="3" t="n">
         <x:v>4.00</x:v>
@@ -405,14 +405,14 @@
     <x:row r="22">
       <x:c r="A22" s="0" t="inlineStr">
         <x:is>
-          <x:t>12.2023</x:t>
+          <x:t>06.2024</x:t>
         </x:is>
       </x:c>
       <x:c r="B22" s="3" t="n">
         <x:v>16.00</x:v>
       </x:c>
       <x:c r="C22" s="3" t="n">
-        <x:v>7.42</x:v>
+        <x:v>8.59</x:v>
       </x:c>
       <x:c r="D22" s="3" t="n">
         <x:v>4.00</x:v>
@@ -421,14 +421,14 @@
     <x:row r="23">
       <x:c r="A23" s="0" t="inlineStr">
         <x:is>
-          <x:t>11.2023</x:t>
+          <x:t>05.2024</x:t>
         </x:is>
       </x:c>
       <x:c r="B23" s="3" t="n">
-        <x:v>15.00</x:v>
+        <x:v>16.00</x:v>
       </x:c>
       <x:c r="C23" s="3" t="n">
-        <x:v>7.48</x:v>
+        <x:v>8.30</x:v>
       </x:c>
       <x:c r="D23" s="3" t="n">
         <x:v>4.00</x:v>
@@ -437,14 +437,14 @@
     <x:row r="24">
       <x:c r="A24" s="0" t="inlineStr">
         <x:is>
-          <x:t>10.2023</x:t>
+          <x:t>04.2024</x:t>
         </x:is>
       </x:c>
       <x:c r="B24" s="3" t="n">
-        <x:v>15.00</x:v>
+        <x:v>16.00</x:v>
       </x:c>
       <x:c r="C24" s="3" t="n">
-        <x:v>6.69</x:v>
+        <x:v>7.84</x:v>
       </x:c>
       <x:c r="D24" s="3" t="n">
         <x:v>4.00</x:v>
@@ -453,14 +453,14 @@
     <x:row r="25">
       <x:c r="A25" s="0" t="inlineStr">
         <x:is>
-          <x:t>09.2023</x:t>
+          <x:t>03.2024</x:t>
         </x:is>
       </x:c>
       <x:c r="B25" s="3" t="n">
-        <x:v>13.00</x:v>
+        <x:v>16.00</x:v>
       </x:c>
       <x:c r="C25" s="3" t="n">
-        <x:v>6.00</x:v>
+        <x:v>7.72</x:v>
       </x:c>
       <x:c r="D25" s="3" t="n">
         <x:v>4.00</x:v>
@@ -469,14 +469,14 @@
     <x:row r="26">
       <x:c r="A26" s="0" t="inlineStr">
         <x:is>
-          <x:t>08.2023</x:t>
+          <x:t>02.2024</x:t>
         </x:is>
       </x:c>
       <x:c r="B26" s="3" t="n">
-        <x:v>12.00</x:v>
+        <x:v>16.00</x:v>
       </x:c>
       <x:c r="C26" s="3" t="n">
-        <x:v>5.15</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="D26" s="3" t="n">
         <x:v>4.00</x:v>
@@ -485,14 +485,14 @@
     <x:row r="27">
       <x:c r="A27" s="0" t="inlineStr">
         <x:is>
-          <x:t>07.2023</x:t>
+          <x:t>01.2024</x:t>
         </x:is>
       </x:c>
       <x:c r="B27" s="3" t="n">
-        <x:v>8.50</x:v>
+        <x:v>16.00</x:v>
       </x:c>
       <x:c r="C27" s="3" t="n">
-        <x:v>4.30</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="D27" s="3" t="n">
         <x:v>4.00</x:v>
@@ -501,14 +501,14 @@
     <x:row r="28">
       <x:c r="A28" s="0" t="inlineStr">
         <x:is>
-          <x:t>06.2023</x:t>
+          <x:t>12.2023</x:t>
         </x:is>
       </x:c>
       <x:c r="B28" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>16.00</x:v>
       </x:c>
       <x:c r="C28" s="3" t="n">
-        <x:v>3.25</x:v>
+        <x:v>7.42</x:v>
       </x:c>
       <x:c r="D28" s="3" t="n">
         <x:v>4.00</x:v>
@@ -517,14 +517,14 @@
     <x:row r="29">
       <x:c r="A29" s="0" t="inlineStr">
         <x:is>
-          <x:t>05.2023</x:t>
+          <x:t>11.2023</x:t>
         </x:is>
       </x:c>
       <x:c r="B29" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>15.00</x:v>
       </x:c>
       <x:c r="C29" s="3" t="n">
-        <x:v>2.51</x:v>
+        <x:v>7.48</x:v>
       </x:c>
       <x:c r="D29" s="3" t="n">
         <x:v>4.00</x:v>
@@ -533,14 +533,14 @@
     <x:row r="30">
       <x:c r="A30" s="0" t="inlineStr">
         <x:is>
-          <x:t>04.2023</x:t>
+          <x:t>10.2023</x:t>
         </x:is>
       </x:c>
       <x:c r="B30" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>15.00</x:v>
       </x:c>
       <x:c r="C30" s="3" t="n">
-        <x:v>2.31</x:v>
+        <x:v>6.69</x:v>
       </x:c>
       <x:c r="D30" s="3" t="n">
         <x:v>4.00</x:v>
@@ -549,14 +549,14 @@
     <x:row r="31">
       <x:c r="A31" s="0" t="inlineStr">
         <x:is>
-          <x:t>03.2023</x:t>
+          <x:t>09.2023</x:t>
         </x:is>
       </x:c>
       <x:c r="B31" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>13.00</x:v>
       </x:c>
       <x:c r="C31" s="3" t="n">
-        <x:v>3.51</x:v>
+        <x:v>6.00</x:v>
       </x:c>
       <x:c r="D31" s="3" t="n">
         <x:v>4.00</x:v>
@@ -565,14 +565,14 @@
     <x:row r="32">
       <x:c r="A32" s="0" t="inlineStr">
         <x:is>
-          <x:t>02.2023</x:t>
+          <x:t>08.2023</x:t>
         </x:is>
       </x:c>
       <x:c r="B32" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>12.00</x:v>
       </x:c>
       <x:c r="C32" s="3" t="n">
-        <x:v>10.99</x:v>
+        <x:v>5.15</x:v>
       </x:c>
       <x:c r="D32" s="3" t="n">
         <x:v>4.00</x:v>
@@ -581,14 +581,14 @@
     <x:row r="33">
       <x:c r="A33" s="0" t="inlineStr">
         <x:is>
-          <x:t>01.2023</x:t>
+          <x:t>07.2023</x:t>
         </x:is>
       </x:c>
       <x:c r="B33" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>8.50</x:v>
       </x:c>
       <x:c r="C33" s="3" t="n">
-        <x:v>11.77</x:v>
+        <x:v>4.30</x:v>
       </x:c>
       <x:c r="D33" s="3" t="n">
         <x:v>4.00</x:v>
@@ -597,14 +597,14 @@
     <x:row r="34">
       <x:c r="A34" s="0" t="inlineStr">
         <x:is>
-          <x:t>12.2022</x:t>
+          <x:t>06.2023</x:t>
         </x:is>
       </x:c>
       <x:c r="B34" s="3" t="n">
         <x:v>7.50</x:v>
       </x:c>
       <x:c r="C34" s="3" t="n">
-        <x:v>11.94</x:v>
+        <x:v>3.25</x:v>
       </x:c>
       <x:c r="D34" s="3" t="n">
         <x:v>4.00</x:v>
@@ -613,14 +613,14 @@
     <x:row r="35">
       <x:c r="A35" s="0" t="inlineStr">
         <x:is>
-          <x:t>11.2022</x:t>
+          <x:t>05.2023</x:t>
         </x:is>
       </x:c>
       <x:c r="B35" s="3" t="n">
         <x:v>7.50</x:v>
       </x:c>
       <x:c r="C35" s="3" t="n">
-        <x:v>11.98</x:v>
+        <x:v>2.51</x:v>
       </x:c>
       <x:c r="D35" s="3" t="n">
         <x:v>4.00</x:v>
@@ -629,14 +629,14 @@
     <x:row r="36">
       <x:c r="A36" s="0" t="inlineStr">
         <x:is>
-          <x:t>10.2022</x:t>
+          <x:t>04.2023</x:t>
         </x:is>
       </x:c>
       <x:c r="B36" s="3" t="n">
         <x:v>7.50</x:v>
       </x:c>
       <x:c r="C36" s="3" t="n">
-        <x:v>12.63</x:v>
+        <x:v>2.31</x:v>
       </x:c>
       <x:c r="D36" s="3" t="n">
         <x:v>4.00</x:v>
@@ -645,14 +645,14 @@
     <x:row r="37">
       <x:c r="A37" s="0" t="inlineStr">
         <x:is>
-          <x:t>09.2022</x:t>
+          <x:t>03.2023</x:t>
         </x:is>
       </x:c>
       <x:c r="B37" s="3" t="n">
         <x:v>7.50</x:v>
       </x:c>
       <x:c r="C37" s="3" t="n">
-        <x:v>13.68</x:v>
+        <x:v>3.51</x:v>
       </x:c>
       <x:c r="D37" s="3" t="n">
         <x:v>4.00</x:v>
@@ -661,14 +661,14 @@
     <x:row r="38">
       <x:c r="A38" s="0" t="inlineStr">
         <x:is>
-          <x:t>08.2022</x:t>
+          <x:t>02.2023</x:t>
         </x:is>
       </x:c>
       <x:c r="B38" s="3" t="n">
-        <x:v>8.00</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C38" s="3" t="n">
-        <x:v>14.30</x:v>
+        <x:v>10.99</x:v>
       </x:c>
       <x:c r="D38" s="3" t="n">
         <x:v>4.00</x:v>
@@ -677,14 +677,14 @@
     <x:row r="39">
       <x:c r="A39" s="0" t="inlineStr">
         <x:is>
-          <x:t>07.2022</x:t>
+          <x:t>01.2023</x:t>
         </x:is>
       </x:c>
       <x:c r="B39" s="3" t="n">
-        <x:v>8.00</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C39" s="3" t="n">
-        <x:v>15.10</x:v>
+        <x:v>11.77</x:v>
       </x:c>
       <x:c r="D39" s="3" t="n">
         <x:v>4.00</x:v>
@@ -693,14 +693,14 @@
     <x:row r="40">
       <x:c r="A40" s="0" t="inlineStr">
         <x:is>
-          <x:t>06.2022</x:t>
+          <x:t>12.2022</x:t>
         </x:is>
       </x:c>
       <x:c r="B40" s="3" t="n">
-        <x:v>9.50</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C40" s="3" t="n">
-        <x:v>15.90</x:v>
+        <x:v>11.94</x:v>
       </x:c>
       <x:c r="D40" s="3" t="n">
         <x:v>4.00</x:v>
@@ -709,14 +709,14 @@
     <x:row r="41">
       <x:c r="A41" s="0" t="inlineStr">
         <x:is>
-          <x:t>05.2022</x:t>
+          <x:t>11.2022</x:t>
         </x:is>
       </x:c>
       <x:c r="B41" s="3" t="n">
-        <x:v>11.00</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C41" s="3" t="n">
-        <x:v>17.10</x:v>
+        <x:v>11.98</x:v>
       </x:c>
       <x:c r="D41" s="3" t="n">
         <x:v>4.00</x:v>
@@ -725,14 +725,14 @@
     <x:row r="42">
       <x:c r="A42" s="0" t="inlineStr">
         <x:is>
-          <x:t>04.2022</x:t>
+          <x:t>10.2022</x:t>
         </x:is>
       </x:c>
       <x:c r="B42" s="3" t="n">
-        <x:v>17.00</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C42" s="3" t="n">
-        <x:v>17.83</x:v>
+        <x:v>12.63</x:v>
       </x:c>
       <x:c r="D42" s="3" t="n">
         <x:v>4.00</x:v>
@@ -741,14 +741,14 @@
     <x:row r="43">
       <x:c r="A43" s="0" t="inlineStr">
         <x:is>
-          <x:t>03.2022</x:t>
+          <x:t>09.2022</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="3" t="n">
-        <x:v>20.00</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C43" s="3" t="n">
-        <x:v>16.69</x:v>
+        <x:v>13.68</x:v>
       </x:c>
       <x:c r="D43" s="3" t="n">
         <x:v>4.00</x:v>
@@ -757,14 +757,14 @@
     <x:row r="44">
       <x:c r="A44" s="0" t="inlineStr">
         <x:is>
-          <x:t>02.2022</x:t>
+          <x:t>08.2022</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="3" t="n">
-        <x:v>20.00</x:v>
+        <x:v>8.00</x:v>
       </x:c>
       <x:c r="C44" s="3" t="n">
-        <x:v>9.15</x:v>
+        <x:v>14.30</x:v>
       </x:c>
       <x:c r="D44" s="3" t="n">
         <x:v>4.00</x:v>
@@ -773,14 +773,14 @@
     <x:row r="45">
       <x:c r="A45" s="0" t="inlineStr">
         <x:is>
-          <x:t>01.2022</x:t>
+          <x:t>07.2022</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="3" t="n">
-        <x:v>8.50</x:v>
+        <x:v>8.00</x:v>
       </x:c>
       <x:c r="C45" s="3" t="n">
-        <x:v>8.73</x:v>
+        <x:v>15.10</x:v>
       </x:c>
       <x:c r="D45" s="3" t="n">
         <x:v>4.00</x:v>
@@ -789,14 +789,14 @@
     <x:row r="46">
       <x:c r="A46" s="0" t="inlineStr">
         <x:is>
-          <x:t>12.2021</x:t>
+          <x:t>06.2022</x:t>
         </x:is>
       </x:c>
       <x:c r="B46" s="3" t="n">
-        <x:v>8.50</x:v>
+        <x:v>9.50</x:v>
       </x:c>
       <x:c r="C46" s="3" t="n">
-        <x:v>8.39</x:v>
+        <x:v>15.90</x:v>
       </x:c>
       <x:c r="D46" s="3" t="n">
         <x:v>4.00</x:v>
@@ -805,14 +805,14 @@
     <x:row r="47">
       <x:c r="A47" s="0" t="inlineStr">
         <x:is>
-          <x:t>11.2021</x:t>
+          <x:t>05.2022</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>11.00</x:v>
       </x:c>
       <x:c r="C47" s="3" t="n">
-        <x:v>8.40</x:v>
+        <x:v>17.10</x:v>
       </x:c>
       <x:c r="D47" s="3" t="n">
         <x:v>4.00</x:v>
@@ -821,14 +821,14 @@
     <x:row r="48">
       <x:c r="A48" s="0" t="inlineStr">
         <x:is>
-          <x:t>10.2021</x:t>
+          <x:t>04.2022</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>17.00</x:v>
       </x:c>
       <x:c r="C48" s="3" t="n">
-        <x:v>8.13</x:v>
+        <x:v>17.83</x:v>
       </x:c>
       <x:c r="D48" s="3" t="n">
         <x:v>4.00</x:v>
@@ -837,14 +837,14 @@
     <x:row r="49">
       <x:c r="A49" s="0" t="inlineStr">
         <x:is>
-          <x:t>09.2021</x:t>
+          <x:t>03.2022</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="3" t="n">
-        <x:v>6.75</x:v>
+        <x:v>20.00</x:v>
       </x:c>
       <x:c r="C49" s="3" t="n">
-        <x:v>7.40</x:v>
+        <x:v>16.69</x:v>
       </x:c>
       <x:c r="D49" s="3" t="n">
         <x:v>4.00</x:v>
@@ -853,14 +853,14 @@
     <x:row r="50">
       <x:c r="A50" s="0" t="inlineStr">
         <x:is>
-          <x:t>08.2021</x:t>
+          <x:t>02.2022</x:t>
         </x:is>
       </x:c>
       <x:c r="B50" s="3" t="n">
-        <x:v>6.50</x:v>
+        <x:v>20.00</x:v>
       </x:c>
       <x:c r="C50" s="3" t="n">
-        <x:v>6.68</x:v>
+        <x:v>9.15</x:v>
       </x:c>
       <x:c r="D50" s="3" t="n">
         <x:v>4.00</x:v>
@@ -869,14 +869,14 @@
     <x:row r="51">
       <x:c r="A51" s="0" t="inlineStr">
         <x:is>
-          <x:t>07.2021</x:t>
+          <x:t>01.2022</x:t>
         </x:is>
       </x:c>
       <x:c r="B51" s="3" t="n">
-        <x:v>6.50</x:v>
+        <x:v>8.50</x:v>
       </x:c>
       <x:c r="C51" s="3" t="n">
-        <x:v>6.50</x:v>
+        <x:v>8.73</x:v>
       </x:c>
       <x:c r="D51" s="3" t="n">
         <x:v>4.00</x:v>
@@ -885,14 +885,14 @@
     <x:row r="52">
       <x:c r="A52" s="0" t="inlineStr">
         <x:is>
-          <x:t>06.2021</x:t>
+          <x:t>12.2021</x:t>
         </x:is>
       </x:c>
       <x:c r="B52" s="3" t="n">
-        <x:v>5.50</x:v>
+        <x:v>8.50</x:v>
       </x:c>
       <x:c r="C52" s="3" t="n">
-        <x:v>6.50</x:v>
+        <x:v>8.39</x:v>
       </x:c>
       <x:c r="D52" s="3" t="n">
         <x:v>4.00</x:v>
@@ -901,14 +901,14 @@
     <x:row r="53">
       <x:c r="A53" s="0" t="inlineStr">
         <x:is>
-          <x:t>05.2021</x:t>
+          <x:t>11.2021</x:t>
         </x:is>
       </x:c>
       <x:c r="B53" s="3" t="n">
-        <x:v>5.00</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C53" s="3" t="n">
-        <x:v>6.00</x:v>
+        <x:v>8.40</x:v>
       </x:c>
       <x:c r="D53" s="3" t="n">
         <x:v>4.00</x:v>
@@ -917,14 +917,14 @@
     <x:row r="54">
       <x:c r="A54" s="0" t="inlineStr">
         <x:is>
-          <x:t>04.2021</x:t>
+          <x:t>10.2021</x:t>
         </x:is>
       </x:c>
       <x:c r="B54" s="3" t="n">
-        <x:v>5.00</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C54" s="3" t="n">
-        <x:v>5.50</x:v>
+        <x:v>8.13</x:v>
       </x:c>
       <x:c r="D54" s="3" t="n">
         <x:v>4.00</x:v>
@@ -933,14 +933,14 @@
     <x:row r="55">
       <x:c r="A55" s="0" t="inlineStr">
         <x:is>
-          <x:t>03.2021</x:t>
+          <x:t>09.2021</x:t>
         </x:is>
       </x:c>
       <x:c r="B55" s="3" t="n">
-        <x:v>4.50</x:v>
+        <x:v>6.75</x:v>
       </x:c>
       <x:c r="C55" s="3" t="n">
-        <x:v>5.80</x:v>
+        <x:v>7.40</x:v>
       </x:c>
       <x:c r="D55" s="3" t="n">
         <x:v>4.00</x:v>
@@ -949,14 +949,14 @@
     <x:row r="56">
       <x:c r="A56" s="0" t="inlineStr">
         <x:is>
-          <x:t>02.2021</x:t>
+          <x:t>08.2021</x:t>
         </x:is>
       </x:c>
       <x:c r="B56" s="3" t="n">
-        <x:v>4.25</x:v>
+        <x:v>6.50</x:v>
       </x:c>
       <x:c r="C56" s="3" t="n">
-        <x:v>5.70</x:v>
+        <x:v>6.68</x:v>
       </x:c>
       <x:c r="D56" s="3" t="n">
         <x:v>4.00</x:v>
@@ -965,14 +965,14 @@
     <x:row r="57">
       <x:c r="A57" s="0" t="inlineStr">
         <x:is>
-          <x:t>01.2021</x:t>
+          <x:t>07.2021</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="3" t="n">
-        <x:v>4.25</x:v>
+        <x:v>6.50</x:v>
       </x:c>
       <x:c r="C57" s="3" t="n">
-        <x:v>5.20</x:v>
+        <x:v>6.50</x:v>
       </x:c>
       <x:c r="D57" s="3" t="n">
         <x:v>4.00</x:v>
@@ -981,14 +981,14 @@
     <x:row r="58">
       <x:c r="A58" s="0" t="inlineStr">
         <x:is>
-          <x:t>12.2020</x:t>
+          <x:t>06.2021</x:t>
         </x:is>
       </x:c>
       <x:c r="B58" s="3" t="n">
-        <x:v>4.25</x:v>
+        <x:v>5.50</x:v>
       </x:c>
       <x:c r="C58" s="3" t="n">
-        <x:v>4.90</x:v>
+        <x:v>6.50</x:v>
       </x:c>
       <x:c r="D58" s="3" t="n">
         <x:v>4.00</x:v>
@@ -997,14 +997,14 @@
     <x:row r="59">
       <x:c r="A59" s="0" t="inlineStr">
         <x:is>
-          <x:t>11.2020</x:t>
+          <x:t>05.2021</x:t>
         </x:is>
       </x:c>
       <x:c r="B59" s="3" t="n">
-        <x:v>4.25</x:v>
+        <x:v>5.00</x:v>
       </x:c>
       <x:c r="C59" s="3" t="n">
-        <x:v>4.40</x:v>
+        <x:v>6.00</x:v>
       </x:c>
       <x:c r="D59" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1013,14 +1013,14 @@
     <x:row r="60">
       <x:c r="A60" s="0" t="inlineStr">
         <x:is>
-          <x:t>10.2020</x:t>
+          <x:t>04.2021</x:t>
         </x:is>
       </x:c>
       <x:c r="B60" s="3" t="n">
-        <x:v>4.25</x:v>
+        <x:v>5.00</x:v>
       </x:c>
       <x:c r="C60" s="3" t="n">
-        <x:v>4.00</x:v>
+        <x:v>5.50</x:v>
       </x:c>
       <x:c r="D60" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1029,14 +1029,14 @@
     <x:row r="61">
       <x:c r="A61" s="0" t="inlineStr">
         <x:is>
-          <x:t>09.2020</x:t>
+          <x:t>03.2021</x:t>
         </x:is>
       </x:c>
       <x:c r="B61" s="3" t="n">
-        <x:v>4.25</x:v>
+        <x:v>4.50</x:v>
       </x:c>
       <x:c r="C61" s="3" t="n">
-        <x:v>3.70</x:v>
+        <x:v>5.80</x:v>
       </x:c>
       <x:c r="D61" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1045,14 +1045,14 @@
     <x:row r="62">
       <x:c r="A62" s="0" t="inlineStr">
         <x:is>
-          <x:t>08.2020</x:t>
+          <x:t>02.2021</x:t>
         </x:is>
       </x:c>
       <x:c r="B62" s="3" t="n">
         <x:v>4.25</x:v>
       </x:c>
       <x:c r="C62" s="3" t="n">
-        <x:v>3.60</x:v>
+        <x:v>5.70</x:v>
       </x:c>
       <x:c r="D62" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1061,14 +1061,14 @@
     <x:row r="63">
       <x:c r="A63" s="0" t="inlineStr">
         <x:is>
-          <x:t>07.2020</x:t>
+          <x:t>01.2021</x:t>
         </x:is>
       </x:c>
       <x:c r="B63" s="3" t="n">
         <x:v>4.25</x:v>
       </x:c>
       <x:c r="C63" s="3" t="n">
-        <x:v>3.40</x:v>
+        <x:v>5.20</x:v>
       </x:c>
       <x:c r="D63" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1077,14 +1077,14 @@
     <x:row r="64">
       <x:c r="A64" s="0" t="inlineStr">
         <x:is>
-          <x:t>06.2020</x:t>
+          <x:t>12.2020</x:t>
         </x:is>
       </x:c>
       <x:c r="B64" s="3" t="n">
-        <x:v>4.50</x:v>
+        <x:v>4.25</x:v>
       </x:c>
       <x:c r="C64" s="3" t="n">
-        <x:v>3.20</x:v>
+        <x:v>4.90</x:v>
       </x:c>
       <x:c r="D64" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1093,14 +1093,14 @@
     <x:row r="65">
       <x:c r="A65" s="0" t="inlineStr">
         <x:is>
-          <x:t>05.2020</x:t>
+          <x:t>11.2020</x:t>
         </x:is>
       </x:c>
       <x:c r="B65" s="3" t="n">
-        <x:v>5.50</x:v>
+        <x:v>4.25</x:v>
       </x:c>
       <x:c r="C65" s="3" t="n">
-        <x:v>3.00</x:v>
+        <x:v>4.40</x:v>
       </x:c>
       <x:c r="D65" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1109,14 +1109,14 @@
     <x:row r="66">
       <x:c r="A66" s="0" t="inlineStr">
         <x:is>
-          <x:t>04.2020</x:t>
+          <x:t>10.2020</x:t>
         </x:is>
       </x:c>
       <x:c r="B66" s="3" t="n">
-        <x:v>5.50</x:v>
+        <x:v>4.25</x:v>
       </x:c>
       <x:c r="C66" s="3" t="n">
-        <x:v>3.10</x:v>
+        <x:v>4.00</x:v>
       </x:c>
       <x:c r="D66" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1125,14 +1125,14 @@
     <x:row r="67">
       <x:c r="A67" s="0" t="inlineStr">
         <x:is>
-          <x:t>03.2020</x:t>
+          <x:t>09.2020</x:t>
         </x:is>
       </x:c>
       <x:c r="B67" s="3" t="n">
-        <x:v>6.00</x:v>
+        <x:v>4.25</x:v>
       </x:c>
       <x:c r="C67" s="3" t="n">
-        <x:v>2.50</x:v>
+        <x:v>3.70</x:v>
       </x:c>
       <x:c r="D67" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1141,14 +1141,14 @@
     <x:row r="68">
       <x:c r="A68" s="0" t="inlineStr">
         <x:is>
-          <x:t>02.2020</x:t>
+          <x:t>08.2020</x:t>
         </x:is>
       </x:c>
       <x:c r="B68" s="3" t="n">
-        <x:v>6.00</x:v>
+        <x:v>4.25</x:v>
       </x:c>
       <x:c r="C68" s="3" t="n">
-        <x:v>2.30</x:v>
+        <x:v>3.60</x:v>
       </x:c>
       <x:c r="D68" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1157,14 +1157,14 @@
     <x:row r="69">
       <x:c r="A69" s="0" t="inlineStr">
         <x:is>
-          <x:t>01.2020</x:t>
+          <x:t>07.2020</x:t>
         </x:is>
       </x:c>
       <x:c r="B69" s="3" t="n">
-        <x:v>6.25</x:v>
+        <x:v>4.25</x:v>
       </x:c>
       <x:c r="C69" s="3" t="n">
-        <x:v>2.40</x:v>
+        <x:v>3.40</x:v>
       </x:c>
       <x:c r="D69" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1173,14 +1173,14 @@
     <x:row r="70">
       <x:c r="A70" s="0" t="inlineStr">
         <x:is>
-          <x:t>12.2019</x:t>
+          <x:t>06.2020</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="3" t="n">
-        <x:v>6.25</x:v>
+        <x:v>4.50</x:v>
       </x:c>
       <x:c r="C70" s="3" t="n">
-        <x:v>3.00</x:v>
+        <x:v>3.20</x:v>
       </x:c>
       <x:c r="D70" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1189,14 +1189,14 @@
     <x:row r="71">
       <x:c r="A71" s="0" t="inlineStr">
         <x:is>
-          <x:t>11.2019</x:t>
+          <x:t>05.2020</x:t>
         </x:is>
       </x:c>
       <x:c r="B71" s="3" t="n">
-        <x:v>6.50</x:v>
+        <x:v>5.50</x:v>
       </x:c>
       <x:c r="C71" s="3" t="n">
-        <x:v>3.50</x:v>
+        <x:v>3.00</x:v>
       </x:c>
       <x:c r="D71" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1205,14 +1205,14 @@
     <x:row r="72">
       <x:c r="A72" s="0" t="inlineStr">
         <x:is>
-          <x:t>10.2019</x:t>
+          <x:t>04.2020</x:t>
         </x:is>
       </x:c>
       <x:c r="B72" s="3" t="n">
-        <x:v>6.50</x:v>
+        <x:v>5.50</x:v>
       </x:c>
       <x:c r="C72" s="3" t="n">
-        <x:v>3.80</x:v>
+        <x:v>3.10</x:v>
       </x:c>
       <x:c r="D72" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1221,14 +1221,14 @@
     <x:row r="73">
       <x:c r="A73" s="0" t="inlineStr">
         <x:is>
-          <x:t>09.2019</x:t>
+          <x:t>03.2020</x:t>
         </x:is>
       </x:c>
       <x:c r="B73" s="3" t="n">
-        <x:v>7.00</x:v>
+        <x:v>6.00</x:v>
       </x:c>
       <x:c r="C73" s="3" t="n">
-        <x:v>4.00</x:v>
+        <x:v>2.50</x:v>
       </x:c>
       <x:c r="D73" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1237,14 +1237,14 @@
     <x:row r="74">
       <x:c r="A74" s="0" t="inlineStr">
         <x:is>
-          <x:t>08.2019</x:t>
+          <x:t>02.2020</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="3" t="n">
-        <x:v>7.25</x:v>
+        <x:v>6.00</x:v>
       </x:c>
       <x:c r="C74" s="3" t="n">
-        <x:v>4.30</x:v>
+        <x:v>2.30</x:v>
       </x:c>
       <x:c r="D74" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1253,14 +1253,14 @@
     <x:row r="75">
       <x:c r="A75" s="0" t="inlineStr">
         <x:is>
-          <x:t>07.2019</x:t>
+          <x:t>01.2020</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="3" t="n">
-        <x:v>7.25</x:v>
+        <x:v>6.25</x:v>
       </x:c>
       <x:c r="C75" s="3" t="n">
-        <x:v>4.60</x:v>
+        <x:v>2.40</x:v>
       </x:c>
       <x:c r="D75" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1269,14 +1269,14 @@
     <x:row r="76">
       <x:c r="A76" s="0" t="inlineStr">
         <x:is>
-          <x:t>06.2019</x:t>
+          <x:t>12.2019</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>6.25</x:v>
       </x:c>
       <x:c r="C76" s="3" t="n">
-        <x:v>4.70</x:v>
+        <x:v>3.00</x:v>
       </x:c>
       <x:c r="D76" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1285,14 +1285,14 @@
     <x:row r="77">
       <x:c r="A77" s="0" t="inlineStr">
         <x:is>
-          <x:t>05.2019</x:t>
+          <x:t>11.2019</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="3" t="n">
-        <x:v>7.75</x:v>
+        <x:v>6.50</x:v>
       </x:c>
       <x:c r="C77" s="3" t="n">
-        <x:v>5.10</x:v>
+        <x:v>3.50</x:v>
       </x:c>
       <x:c r="D77" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1301,14 +1301,14 @@
     <x:row r="78">
       <x:c r="A78" s="0" t="inlineStr">
         <x:is>
-          <x:t>04.2019</x:t>
+          <x:t>10.2019</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="3" t="n">
-        <x:v>7.75</x:v>
+        <x:v>6.50</x:v>
       </x:c>
       <x:c r="C78" s="3" t="n">
-        <x:v>5.20</x:v>
+        <x:v>3.80</x:v>
       </x:c>
       <x:c r="D78" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1317,14 +1317,14 @@
     <x:row r="79">
       <x:c r="A79" s="0" t="inlineStr">
         <x:is>
-          <x:t>03.2019</x:t>
+          <x:t>09.2019</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="3" t="n">
-        <x:v>7.75</x:v>
+        <x:v>7.00</x:v>
       </x:c>
       <x:c r="C79" s="3" t="n">
-        <x:v>5.30</x:v>
+        <x:v>4.00</x:v>
       </x:c>
       <x:c r="D79" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1333,14 +1333,14 @@
     <x:row r="80">
       <x:c r="A80" s="0" t="inlineStr">
         <x:is>
-          <x:t>02.2019</x:t>
+          <x:t>08.2019</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="3" t="n">
-        <x:v>7.75</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="C80" s="3" t="n">
-        <x:v>5.20</x:v>
+        <x:v>4.30</x:v>
       </x:c>
       <x:c r="D80" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1349,14 +1349,14 @@
     <x:row r="81">
       <x:c r="A81" s="0" t="inlineStr">
         <x:is>
-          <x:t>01.2019</x:t>
+          <x:t>07.2019</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="3" t="n">
-        <x:v>7.75</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="C81" s="3" t="n">
-        <x:v>5.00</x:v>
+        <x:v>4.60</x:v>
       </x:c>
       <x:c r="D81" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1365,14 +1365,14 @@
     <x:row r="82">
       <x:c r="A82" s="0" t="inlineStr">
         <x:is>
-          <x:t>12.2018</x:t>
+          <x:t>06.2019</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="3" t="n">
-        <x:v>7.75</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C82" s="3" t="n">
-        <x:v>4.30</x:v>
+        <x:v>4.70</x:v>
       </x:c>
       <x:c r="D82" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1381,14 +1381,14 @@
     <x:row r="83">
       <x:c r="A83" s="0" t="inlineStr">
         <x:is>
-          <x:t>11.2018</x:t>
+          <x:t>05.2019</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>7.75</x:v>
       </x:c>
       <x:c r="C83" s="3" t="n">
-        <x:v>3.80</x:v>
+        <x:v>5.10</x:v>
       </x:c>
       <x:c r="D83" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1397,14 +1397,14 @@
     <x:row r="84">
       <x:c r="A84" s="0" t="inlineStr">
         <x:is>
-          <x:t>10.2018</x:t>
+          <x:t>04.2019</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>7.75</x:v>
       </x:c>
       <x:c r="C84" s="3" t="n">
-        <x:v>3.50</x:v>
+        <x:v>5.20</x:v>
       </x:c>
       <x:c r="D84" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1413,14 +1413,14 @@
     <x:row r="85">
       <x:c r="A85" s="0" t="inlineStr">
         <x:is>
-          <x:t>09.2018</x:t>
+          <x:t>03.2019</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>7.75</x:v>
       </x:c>
       <x:c r="C85" s="3" t="n">
-        <x:v>3.40</x:v>
+        <x:v>5.30</x:v>
       </x:c>
       <x:c r="D85" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1429,14 +1429,14 @@
     <x:row r="86">
       <x:c r="A86" s="0" t="inlineStr">
         <x:is>
-          <x:t>08.2018</x:t>
+          <x:t>02.2019</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="3" t="n">
-        <x:v>7.25</x:v>
+        <x:v>7.75</x:v>
       </x:c>
       <x:c r="C86" s="3" t="n">
-        <x:v>3.10</x:v>
+        <x:v>5.20</x:v>
       </x:c>
       <x:c r="D86" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1445,14 +1445,14 @@
     <x:row r="87">
       <x:c r="A87" s="0" t="inlineStr">
         <x:is>
-          <x:t>07.2018</x:t>
+          <x:t>01.2019</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="3" t="n">
-        <x:v>7.25</x:v>
+        <x:v>7.75</x:v>
       </x:c>
       <x:c r="C87" s="3" t="n">
-        <x:v>2.50</x:v>
+        <x:v>5.00</x:v>
       </x:c>
       <x:c r="D87" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1461,14 +1461,14 @@
     <x:row r="88">
       <x:c r="A88" s="0" t="inlineStr">
         <x:is>
-          <x:t>06.2018</x:t>
+          <x:t>12.2018</x:t>
         </x:is>
       </x:c>
       <x:c r="B88" s="3" t="n">
-        <x:v>7.25</x:v>
+        <x:v>7.75</x:v>
       </x:c>
       <x:c r="C88" s="3" t="n">
-        <x:v>2.30</x:v>
+        <x:v>4.30</x:v>
       </x:c>
       <x:c r="D88" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1477,14 +1477,14 @@
     <x:row r="89">
       <x:c r="A89" s="0" t="inlineStr">
         <x:is>
-          <x:t>05.2018</x:t>
+          <x:t>11.2018</x:t>
         </x:is>
       </x:c>
       <x:c r="B89" s="3" t="n">
-        <x:v>7.25</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C89" s="3" t="n">
-        <x:v>2.40</x:v>
+        <x:v>3.80</x:v>
       </x:c>
       <x:c r="D89" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1493,14 +1493,14 @@
     <x:row r="90">
       <x:c r="A90" s="0" t="inlineStr">
         <x:is>
-          <x:t>04.2018</x:t>
+          <x:t>10.2018</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="3" t="n">
-        <x:v>7.25</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C90" s="3" t="n">
-        <x:v>2.40</x:v>
+        <x:v>3.50</x:v>
       </x:c>
       <x:c r="D90" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1509,14 +1509,14 @@
     <x:row r="91">
       <x:c r="A91" s="0" t="inlineStr">
         <x:is>
-          <x:t>03.2018</x:t>
+          <x:t>09.2018</x:t>
         </x:is>
       </x:c>
       <x:c r="B91" s="3" t="n">
-        <x:v>7.25</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C91" s="3" t="n">
-        <x:v>2.40</x:v>
+        <x:v>3.40</x:v>
       </x:c>
       <x:c r="D91" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1525,14 +1525,14 @@
     <x:row r="92">
       <x:c r="A92" s="0" t="inlineStr">
         <x:is>
-          <x:t>02.2018</x:t>
+          <x:t>08.2018</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="C92" s="3" t="n">
-        <x:v>2.20</x:v>
+        <x:v>3.10</x:v>
       </x:c>
       <x:c r="D92" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1541,14 +1541,14 @@
     <x:row r="93">
       <x:c r="A93" s="0" t="inlineStr">
         <x:is>
-          <x:t>01.2018</x:t>
+          <x:t>07.2018</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="3" t="n">
-        <x:v>7.75</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="C93" s="3" t="n">
-        <x:v>2.20</x:v>
+        <x:v>2.50</x:v>
       </x:c>
       <x:c r="D93" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1557,14 +1557,14 @@
     <x:row r="94">
       <x:c r="A94" s="0" t="inlineStr">
         <x:is>
-          <x:t>12.2017</x:t>
+          <x:t>06.2018</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="3" t="n">
-        <x:v>7.75</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="C94" s="3" t="n">
-        <x:v>2.50</x:v>
+        <x:v>2.30</x:v>
       </x:c>
       <x:c r="D94" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1573,14 +1573,14 @@
     <x:row r="95">
       <x:c r="A95" s="0" t="inlineStr">
         <x:is>
-          <x:t>11.2017</x:t>
+          <x:t>05.2018</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" s="3" t="n">
-        <x:v>8.25</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="C95" s="3" t="n">
-        <x:v>2.50</x:v>
+        <x:v>2.40</x:v>
       </x:c>
       <x:c r="D95" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1589,14 +1589,14 @@
     <x:row r="96">
       <x:c r="A96" s="0" t="inlineStr">
         <x:is>
-          <x:t>10.2017</x:t>
+          <x:t>04.2018</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="3" t="n">
-        <x:v>8.25</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="C96" s="3" t="n">
-        <x:v>2.70</x:v>
+        <x:v>2.40</x:v>
       </x:c>
       <x:c r="D96" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1605,14 +1605,14 @@
     <x:row r="97">
       <x:c r="A97" s="0" t="inlineStr">
         <x:is>
-          <x:t>09.2017</x:t>
+          <x:t>03.2018</x:t>
         </x:is>
       </x:c>
       <x:c r="B97" s="3" t="n">
-        <x:v>8.50</x:v>
+        <x:v>7.25</x:v>
       </x:c>
       <x:c r="C97" s="3" t="n">
-        <x:v>3.00</x:v>
+        <x:v>2.40</x:v>
       </x:c>
       <x:c r="D97" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1621,14 +1621,14 @@
     <x:row r="98">
       <x:c r="A98" s="0" t="inlineStr">
         <x:is>
-          <x:t>08.2017</x:t>
+          <x:t>02.2018</x:t>
         </x:is>
       </x:c>
       <x:c r="B98" s="3" t="n">
-        <x:v>9.00</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="C98" s="3" t="n">
-        <x:v>3.30</x:v>
+        <x:v>2.20</x:v>
       </x:c>
       <x:c r="D98" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1637,14 +1637,14 @@
     <x:row r="99">
       <x:c r="A99" s="0" t="inlineStr">
         <x:is>
-          <x:t>07.2017</x:t>
+          <x:t>01.2018</x:t>
         </x:is>
       </x:c>
       <x:c r="B99" s="3" t="n">
-        <x:v>9.00</x:v>
+        <x:v>7.75</x:v>
       </x:c>
       <x:c r="C99" s="3" t="n">
-        <x:v>3.90</x:v>
+        <x:v>2.20</x:v>
       </x:c>
       <x:c r="D99" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1653,14 +1653,14 @@
     <x:row r="100">
       <x:c r="A100" s="0" t="inlineStr">
         <x:is>
-          <x:t>06.2017</x:t>
+          <x:t>12.2017</x:t>
         </x:is>
       </x:c>
       <x:c r="B100" s="3" t="n">
-        <x:v>9.00</x:v>
+        <x:v>7.75</x:v>
       </x:c>
       <x:c r="C100" s="3" t="n">
-        <x:v>4.40</x:v>
+        <x:v>2.50</x:v>
       </x:c>
       <x:c r="D100" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1669,14 +1669,14 @@
     <x:row r="101">
       <x:c r="A101" s="0" t="inlineStr">
         <x:is>
-          <x:t>05.2017</x:t>
+          <x:t>11.2017</x:t>
         </x:is>
       </x:c>
       <x:c r="B101" s="3" t="n">
-        <x:v>9.25</x:v>
+        <x:v>8.25</x:v>
       </x:c>
       <x:c r="C101" s="3" t="n">
-        <x:v>4.10</x:v>
+        <x:v>2.50</x:v>
       </x:c>
       <x:c r="D101" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1685,14 +1685,14 @@
     <x:row r="102">
       <x:c r="A102" s="0" t="inlineStr">
         <x:is>
-          <x:t>04.2017</x:t>
+          <x:t>10.2017</x:t>
         </x:is>
       </x:c>
       <x:c r="B102" s="3" t="n">
-        <x:v>9.75</x:v>
+        <x:v>8.25</x:v>
       </x:c>
       <x:c r="C102" s="3" t="n">
-        <x:v>4.10</x:v>
+        <x:v>2.70</x:v>
       </x:c>
       <x:c r="D102" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1701,14 +1701,14 @@
     <x:row r="103">
       <x:c r="A103" s="0" t="inlineStr">
         <x:is>
-          <x:t>03.2017</x:t>
+          <x:t>09.2017</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" s="3" t="n">
-        <x:v>9.75</x:v>
+        <x:v>8.50</x:v>
       </x:c>
       <x:c r="C103" s="3" t="n">
-        <x:v>4.30</x:v>
+        <x:v>3.00</x:v>
       </x:c>
       <x:c r="D103" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1717,14 +1717,14 @@
     <x:row r="104">
       <x:c r="A104" s="0" t="inlineStr">
         <x:is>
-          <x:t>02.2017</x:t>
+          <x:t>08.2017</x:t>
         </x:is>
       </x:c>
       <x:c r="B104" s="3" t="n">
-        <x:v>10.00</x:v>
+        <x:v>9.00</x:v>
       </x:c>
       <x:c r="C104" s="3" t="n">
-        <x:v>4.60</x:v>
+        <x:v>3.30</x:v>
       </x:c>
       <x:c r="D104" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1733,14 +1733,14 @@
     <x:row r="105">
       <x:c r="A105" s="0" t="inlineStr">
         <x:is>
-          <x:t>01.2017</x:t>
+          <x:t>07.2017</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" s="3" t="n">
-        <x:v>10.00</x:v>
+        <x:v>9.00</x:v>
       </x:c>
       <x:c r="C105" s="3" t="n">
-        <x:v>5.00</x:v>
+        <x:v>3.90</x:v>
       </x:c>
       <x:c r="D105" s="3" t="n">
         <x:v>4.00</x:v>
@@ -1749,506 +1749,658 @@
     <x:row r="106">
       <x:c r="A106" s="0" t="inlineStr">
         <x:is>
-          <x:t>12.2016</x:t>
+          <x:t>06.2017</x:t>
         </x:is>
       </x:c>
       <x:c r="B106" s="3" t="n">
-        <x:v>10.00</x:v>
+        <x:v>9.00</x:v>
       </x:c>
       <x:c r="C106" s="3" t="n">
-        <x:v>5.40</x:v>
-      </x:c>
-      <x:c r="D106"/>
+        <x:v>4.40</x:v>
+      </x:c>
+      <x:c r="D106" s="3" t="n">
+        <x:v>4.00</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="0" t="inlineStr">
         <x:is>
-          <x:t>11.2016</x:t>
+          <x:t>05.2017</x:t>
         </x:is>
       </x:c>
       <x:c r="B107" s="3" t="n">
-        <x:v>10.00</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="C107" s="3" t="n">
-        <x:v>5.80</x:v>
-      </x:c>
-      <x:c r="D107"/>
+        <x:v>4.10</x:v>
+      </x:c>
+      <x:c r="D107" s="3" t="n">
+        <x:v>4.00</x:v>
+      </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="0" t="inlineStr">
         <x:is>
-          <x:t>10.2016</x:t>
+          <x:t>04.2017</x:t>
         </x:is>
       </x:c>
       <x:c r="B108" s="3" t="n">
-        <x:v>10.00</x:v>
+        <x:v>9.75</x:v>
       </x:c>
       <x:c r="C108" s="3" t="n">
-        <x:v>6.10</x:v>
-      </x:c>
-      <x:c r="D108"/>
+        <x:v>4.10</x:v>
+      </x:c>
+      <x:c r="D108" s="3" t="n">
+        <x:v>4.00</x:v>
+      </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="0" t="inlineStr">
         <x:is>
-          <x:t>09.2016</x:t>
+          <x:t>03.2017</x:t>
         </x:is>
       </x:c>
       <x:c r="B109" s="3" t="n">
-        <x:v>10.00</x:v>
+        <x:v>9.75</x:v>
       </x:c>
       <x:c r="C109" s="3" t="n">
-        <x:v>6.40</x:v>
-      </x:c>
-      <x:c r="D109"/>
+        <x:v>4.30</x:v>
+      </x:c>
+      <x:c r="D109" s="3" t="n">
+        <x:v>4.00</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="0" t="inlineStr">
         <x:is>
-          <x:t>08.2016</x:t>
+          <x:t>02.2017</x:t>
         </x:is>
       </x:c>
       <x:c r="B110" s="3" t="n">
-        <x:v>10.50</x:v>
+        <x:v>10.00</x:v>
       </x:c>
       <x:c r="C110" s="3" t="n">
-        <x:v>6.90</x:v>
-      </x:c>
-      <x:c r="D110"/>
+        <x:v>4.60</x:v>
+      </x:c>
+      <x:c r="D110" s="3" t="n">
+        <x:v>4.00</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="0" t="inlineStr">
         <x:is>
-          <x:t>07.2016</x:t>
+          <x:t>01.2017</x:t>
         </x:is>
       </x:c>
       <x:c r="B111" s="3" t="n">
-        <x:v>10.50</x:v>
+        <x:v>10.00</x:v>
       </x:c>
       <x:c r="C111" s="3" t="n">
-        <x:v>7.20</x:v>
-      </x:c>
-      <x:c r="D111"/>
+        <x:v>5.00</x:v>
+      </x:c>
+      <x:c r="D111" s="3" t="n">
+        <x:v>4.00</x:v>
+      </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="0" t="inlineStr">
         <x:is>
-          <x:t>06.2016</x:t>
+          <x:t>12.2016</x:t>
         </x:is>
       </x:c>
       <x:c r="B112" s="3" t="n">
-        <x:v>10.50</x:v>
+        <x:v>10.00</x:v>
       </x:c>
       <x:c r="C112" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>5.40</x:v>
       </x:c>
       <x:c r="D112"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="0" t="inlineStr">
         <x:is>
-          <x:t>05.2016</x:t>
+          <x:t>11.2016</x:t>
         </x:is>
       </x:c>
       <x:c r="B113" s="3" t="n">
-        <x:v>11.00</x:v>
+        <x:v>10.00</x:v>
       </x:c>
       <x:c r="C113" s="3" t="n">
-        <x:v>7.30</x:v>
+        <x:v>5.80</x:v>
       </x:c>
       <x:c r="D113"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="0" t="inlineStr">
         <x:is>
-          <x:t>04.2016</x:t>
+          <x:t>10.2016</x:t>
         </x:is>
       </x:c>
       <x:c r="B114" s="3" t="n">
-        <x:v>11.00</x:v>
+        <x:v>10.00</x:v>
       </x:c>
       <x:c r="C114" s="3" t="n">
-        <x:v>7.30</x:v>
+        <x:v>6.10</x:v>
       </x:c>
       <x:c r="D114"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="0" t="inlineStr">
         <x:is>
-          <x:t>03.2016</x:t>
+          <x:t>09.2016</x:t>
         </x:is>
       </x:c>
       <x:c r="B115" s="3" t="n">
-        <x:v>11.00</x:v>
+        <x:v>10.00</x:v>
       </x:c>
       <x:c r="C115" s="3" t="n">
-        <x:v>7.30</x:v>
+        <x:v>6.40</x:v>
       </x:c>
       <x:c r="D115"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="0" t="inlineStr">
         <x:is>
-          <x:t>02.2016</x:t>
+          <x:t>08.2016</x:t>
         </x:is>
       </x:c>
       <x:c r="B116" s="3" t="n">
-        <x:v>11.00</x:v>
+        <x:v>10.50</x:v>
       </x:c>
       <x:c r="C116" s="3" t="n">
-        <x:v>8.10</x:v>
+        <x:v>6.90</x:v>
       </x:c>
       <x:c r="D116"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="0" t="inlineStr">
         <x:is>
-          <x:t>01.2016</x:t>
+          <x:t>07.2016</x:t>
         </x:is>
       </x:c>
       <x:c r="B117" s="3" t="n">
-        <x:v>11.00</x:v>
+        <x:v>10.50</x:v>
       </x:c>
       <x:c r="C117" s="3" t="n">
-        <x:v>9.80</x:v>
+        <x:v>7.20</x:v>
       </x:c>
       <x:c r="D117"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="0" t="inlineStr">
         <x:is>
-          <x:t>12.2015</x:t>
+          <x:t>06.2016</x:t>
         </x:is>
       </x:c>
       <x:c r="B118" s="3" t="n">
-        <x:v>11.00</x:v>
+        <x:v>10.50</x:v>
       </x:c>
       <x:c r="C118" s="3" t="n">
-        <x:v>12.90</x:v>
+        <x:v>7.50</x:v>
       </x:c>
       <x:c r="D118"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="0" t="inlineStr">
         <x:is>
-          <x:t>11.2015</x:t>
+          <x:t>05.2016</x:t>
         </x:is>
       </x:c>
       <x:c r="B119" s="3" t="n">
         <x:v>11.00</x:v>
       </x:c>
       <x:c r="C119" s="3" t="n">
-        <x:v>15.00</x:v>
+        <x:v>7.30</x:v>
       </x:c>
       <x:c r="D119"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="0" t="inlineStr">
         <x:is>
-          <x:t>10.2015</x:t>
+          <x:t>04.2016</x:t>
         </x:is>
       </x:c>
       <x:c r="B120" s="3" t="n">
         <x:v>11.00</x:v>
       </x:c>
       <x:c r="C120" s="3" t="n">
-        <x:v>15.60</x:v>
+        <x:v>7.30</x:v>
       </x:c>
       <x:c r="D120"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="0" t="inlineStr">
         <x:is>
-          <x:t>09.2015</x:t>
+          <x:t>03.2016</x:t>
         </x:is>
       </x:c>
       <x:c r="B121" s="3" t="n">
         <x:v>11.00</x:v>
       </x:c>
       <x:c r="C121" s="3" t="n">
-        <x:v>15.70</x:v>
+        <x:v>7.30</x:v>
       </x:c>
       <x:c r="D121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="0" t="inlineStr">
         <x:is>
-          <x:t>08.2015</x:t>
+          <x:t>02.2016</x:t>
         </x:is>
       </x:c>
       <x:c r="B122" s="3" t="n">
         <x:v>11.00</x:v>
       </x:c>
       <x:c r="C122" s="3" t="n">
-        <x:v>15.80</x:v>
+        <x:v>8.10</x:v>
       </x:c>
       <x:c r="D122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="0" t="inlineStr">
         <x:is>
-          <x:t>07.2015</x:t>
+          <x:t>01.2016</x:t>
         </x:is>
       </x:c>
       <x:c r="B123" s="3" t="n">
-        <x:v>11.50</x:v>
+        <x:v>11.00</x:v>
       </x:c>
       <x:c r="C123" s="3" t="n">
-        <x:v>15.60</x:v>
+        <x:v>9.80</x:v>
       </x:c>
       <x:c r="D123"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="0" t="inlineStr">
         <x:is>
-          <x:t>06.2015</x:t>
+          <x:t>12.2015</x:t>
         </x:is>
       </x:c>
       <x:c r="B124" s="3" t="n">
-        <x:v>11.50</x:v>
+        <x:v>11.00</x:v>
       </x:c>
       <x:c r="C124" s="3" t="n">
-        <x:v>15.30</x:v>
+        <x:v>12.90</x:v>
       </x:c>
       <x:c r="D124"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="0" t="inlineStr">
         <x:is>
-          <x:t>05.2015</x:t>
+          <x:t>11.2015</x:t>
         </x:is>
       </x:c>
       <x:c r="B125" s="3" t="n">
-        <x:v>12.50</x:v>
+        <x:v>11.00</x:v>
       </x:c>
       <x:c r="C125" s="3" t="n">
-        <x:v>15.80</x:v>
+        <x:v>15.00</x:v>
       </x:c>
       <x:c r="D125"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="0" t="inlineStr">
         <x:is>
-          <x:t>04.2015</x:t>
+          <x:t>10.2015</x:t>
         </x:is>
       </x:c>
       <x:c r="B126" s="3" t="n">
-        <x:v>14.00</x:v>
+        <x:v>11.00</x:v>
       </x:c>
       <x:c r="C126" s="3" t="n">
-        <x:v>16.40</x:v>
+        <x:v>15.60</x:v>
       </x:c>
       <x:c r="D126"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="0" t="inlineStr">
         <x:is>
-          <x:t>03.2015</x:t>
+          <x:t>09.2015</x:t>
         </x:is>
       </x:c>
       <x:c r="B127" s="3" t="n">
-        <x:v>14.00</x:v>
+        <x:v>11.00</x:v>
       </x:c>
       <x:c r="C127" s="3" t="n">
-        <x:v>16.90</x:v>
+        <x:v>15.70</x:v>
       </x:c>
       <x:c r="D127"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="0" t="inlineStr">
         <x:is>
-          <x:t>02.2015</x:t>
+          <x:t>08.2015</x:t>
         </x:is>
       </x:c>
       <x:c r="B128" s="3" t="n">
-        <x:v>15.00</x:v>
+        <x:v>11.00</x:v>
       </x:c>
       <x:c r="C128" s="3" t="n">
-        <x:v>16.70</x:v>
+        <x:v>15.80</x:v>
       </x:c>
       <x:c r="D128"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="0" t="inlineStr">
         <x:is>
-          <x:t>01.2015</x:t>
+          <x:t>07.2015</x:t>
         </x:is>
       </x:c>
       <x:c r="B129" s="3" t="n">
-        <x:v>17.00</x:v>
+        <x:v>11.50</x:v>
       </x:c>
       <x:c r="C129" s="3" t="n">
-        <x:v>14.96</x:v>
+        <x:v>15.60</x:v>
       </x:c>
       <x:c r="D129"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="0" t="inlineStr">
         <x:is>
-          <x:t>12.2014</x:t>
+          <x:t>06.2015</x:t>
         </x:is>
       </x:c>
       <x:c r="B130" s="3" t="n">
-        <x:v>17.00</x:v>
+        <x:v>11.50</x:v>
       </x:c>
       <x:c r="C130" s="3" t="n">
-        <x:v>11.35</x:v>
+        <x:v>15.30</x:v>
       </x:c>
       <x:c r="D130"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="0" t="inlineStr">
         <x:is>
-          <x:t>11.2014</x:t>
+          <x:t>05.2015</x:t>
         </x:is>
       </x:c>
       <x:c r="B131" s="3" t="n">
-        <x:v>9.50</x:v>
+        <x:v>12.50</x:v>
       </x:c>
       <x:c r="C131" s="3" t="n">
-        <x:v>9.06</x:v>
+        <x:v>15.80</x:v>
       </x:c>
       <x:c r="D131"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="0" t="inlineStr">
         <x:is>
-          <x:t>10.2014</x:t>
+          <x:t>04.2015</x:t>
         </x:is>
       </x:c>
       <x:c r="B132" s="3" t="n">
-        <x:v>8.00</x:v>
+        <x:v>14.00</x:v>
       </x:c>
       <x:c r="C132" s="3" t="n">
-        <x:v>8.29</x:v>
+        <x:v>16.40</x:v>
       </x:c>
       <x:c r="D132"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="0" t="inlineStr">
         <x:is>
-          <x:t>09.2014</x:t>
+          <x:t>03.2015</x:t>
         </x:is>
       </x:c>
       <x:c r="B133" s="3" t="n">
-        <x:v>8.00</x:v>
+        <x:v>14.00</x:v>
       </x:c>
       <x:c r="C133" s="3" t="n">
-        <x:v>8.03</x:v>
+        <x:v>16.90</x:v>
       </x:c>
       <x:c r="D133"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="0" t="inlineStr">
         <x:is>
-          <x:t>08.2014</x:t>
+          <x:t>02.2015</x:t>
         </x:is>
       </x:c>
       <x:c r="B134" s="3" t="n">
-        <x:v>8.00</x:v>
+        <x:v>15.00</x:v>
       </x:c>
       <x:c r="C134" s="3" t="n">
-        <x:v>7.55</x:v>
+        <x:v>16.70</x:v>
       </x:c>
       <x:c r="D134"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="0" t="inlineStr">
         <x:is>
-          <x:t>07.2014</x:t>
+          <x:t>01.2015</x:t>
         </x:is>
       </x:c>
       <x:c r="B135" s="3" t="n">
-        <x:v>8.00</x:v>
+        <x:v>17.00</x:v>
       </x:c>
       <x:c r="C135" s="3" t="n">
-        <x:v>7.45</x:v>
+        <x:v>14.96</x:v>
       </x:c>
       <x:c r="D135"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="0" t="inlineStr">
         <x:is>
-          <x:t>06.2014</x:t>
+          <x:t>12.2014</x:t>
         </x:is>
       </x:c>
       <x:c r="B136" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>17.00</x:v>
       </x:c>
       <x:c r="C136" s="3" t="n">
-        <x:v>7.81</x:v>
+        <x:v>11.35</x:v>
       </x:c>
       <x:c r="D136"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="0" t="inlineStr">
         <x:is>
-          <x:t>05.2014</x:t>
+          <x:t>11.2014</x:t>
         </x:is>
       </x:c>
       <x:c r="B137" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>9.50</x:v>
       </x:c>
       <x:c r="C137" s="3" t="n">
-        <x:v>7.59</x:v>
+        <x:v>9.06</x:v>
       </x:c>
       <x:c r="D137"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="0" t="inlineStr">
         <x:is>
-          <x:t>04.2014</x:t>
+          <x:t>10.2014</x:t>
         </x:is>
       </x:c>
       <x:c r="B138" s="3" t="n">
-        <x:v>7.50</x:v>
+        <x:v>8.00</x:v>
       </x:c>
       <x:c r="C138" s="3" t="n">
-        <x:v>7.33</x:v>
+        <x:v>8.29</x:v>
       </x:c>
       <x:c r="D138"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="0" t="inlineStr">
         <x:is>
-          <x:t>03.2014</x:t>
+          <x:t>09.2014</x:t>
         </x:is>
       </x:c>
       <x:c r="B139" s="3" t="n">
-        <x:v>7.00</x:v>
+        <x:v>8.00</x:v>
       </x:c>
       <x:c r="C139" s="3" t="n">
-        <x:v>6.92</x:v>
+        <x:v>8.03</x:v>
       </x:c>
       <x:c r="D139"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="0" t="inlineStr">
         <x:is>
-          <x:t>02.2014</x:t>
+          <x:t>08.2014</x:t>
         </x:is>
       </x:c>
       <x:c r="B140" s="3" t="n">
-        <x:v>5.50</x:v>
+        <x:v>8.00</x:v>
       </x:c>
       <x:c r="C140" s="3" t="n">
-        <x:v>6.21</x:v>
+        <x:v>7.55</x:v>
       </x:c>
       <x:c r="D140"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="0" t="inlineStr">
         <x:is>
+          <x:t>07.2014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B141" s="3" t="n">
+        <x:v>8.00</x:v>
+      </x:c>
+      <x:c r="C141" s="3" t="n">
+        <x:v>7.45</x:v>
+      </x:c>
+      <x:c r="D141"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="0" t="inlineStr">
+        <x:is>
+          <x:t>06.2014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B142" s="3" t="n">
+        <x:v>7.50</x:v>
+      </x:c>
+      <x:c r="C142" s="3" t="n">
+        <x:v>7.81</x:v>
+      </x:c>
+      <x:c r="D142"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="0" t="inlineStr">
+        <x:is>
+          <x:t>05.2014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B143" s="3" t="n">
+        <x:v>7.50</x:v>
+      </x:c>
+      <x:c r="C143" s="3" t="n">
+        <x:v>7.59</x:v>
+      </x:c>
+      <x:c r="D143"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="0" t="inlineStr">
+        <x:is>
+          <x:t>04.2014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B144" s="3" t="n">
+        <x:v>7.50</x:v>
+      </x:c>
+      <x:c r="C144" s="3" t="n">
+        <x:v>7.33</x:v>
+      </x:c>
+      <x:c r="D144"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="0" t="inlineStr">
+        <x:is>
+          <x:t>03.2014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B145" s="3" t="n">
+        <x:v>7.00</x:v>
+      </x:c>
+      <x:c r="C145" s="3" t="n">
+        <x:v>6.92</x:v>
+      </x:c>
+      <x:c r="D145"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="0" t="inlineStr">
+        <x:is>
+          <x:t>02.2014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B146" s="3" t="n">
+        <x:v>5.50</x:v>
+      </x:c>
+      <x:c r="C146" s="3" t="n">
+        <x:v>6.21</x:v>
+      </x:c>
+      <x:c r="D146"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="0" t="inlineStr">
+        <x:is>
           <x:t>01.2014</x:t>
         </x:is>
       </x:c>
-      <x:c r="B141" s="3" t="n">
+      <x:c r="B147" s="3" t="n">
         <x:v>5.50</x:v>
       </x:c>
-      <x:c r="C141" s="3" t="n">
+      <x:c r="C147" s="3" t="n">
         <x:v>6.07</x:v>
       </x:c>
-      <x:c r="D141"/>
+      <x:c r="D147"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="0" t="inlineStr">
+        <x:is>
+          <x:t>12.2013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B148" s="3" t="n">
+        <x:v>5.50</x:v>
+      </x:c>
+      <x:c r="C148" s="3" t="n">
+        <x:v>6.47</x:v>
+      </x:c>
+      <x:c r="D148"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="0" t="inlineStr">
+        <x:is>
+          <x:t>11.2013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B149" s="3" t="n">
+        <x:v>5.50</x:v>
+      </x:c>
+      <x:c r="C149" s="3" t="n">
+        <x:v>6.50</x:v>
+      </x:c>
+      <x:c r="D149"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="0" t="inlineStr">
+        <x:is>
+          <x:t>10.2013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B150" s="3" t="n">
+        <x:v>5.50</x:v>
+      </x:c>
+      <x:c r="C150" s="3" t="n">
+        <x:v>6.27</x:v>
+      </x:c>
+      <x:c r="D150"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="0" t="inlineStr">
+        <x:is>
+          <x:t>09.2013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B151" s="3" t="n">
+        <x:v>5.50</x:v>
+      </x:c>
+      <x:c r="C151" s="3" t="n">
+        <x:v>6.14</x:v>
+      </x:c>
+      <x:c r="D151"/>
     </x:row>
   </x:sheetData>
 </x:worksheet>
